--- a/ig/nr-change-mss-Org/StructureDefinition-as-organization.xlsx
+++ b/ig/nr-change-mss-Org/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-15T11:25:47+00:00</t>
+    <t>2023-06-15T14:56:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1580,13 +1580,13 @@
 </t>
   </si>
   <si>
-    <t>Point de contact.</t>
+    <t>Contact for the organization for a certain purpose</t>
   </si>
   <si>
     <t>Contact for the organization for a certain purpose.</t>
   </si>
   <si>
-    <t>Personne ou service agissant comme point de contact auprès d'une autre personne ou d'un autre service.</t>
+    <t>Where multiple contacts for the same purpose are provided there is a standard extension that can be used to determine which one is the preferred contact to use.</t>
   </si>
   <si>
     <t>Need to keep track of assigned contact points within bigger organization.</t>
@@ -11511,7 +11511,7 @@
         <v>37</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>35</v>
@@ -12433,7 +12433,7 @@
         <v>37</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>35</v>

--- a/ig/nr-change-mss-Org/StructureDefinition-as-organization.xlsx
+++ b/ig/nr-change-mss-Org/StructureDefinition-as-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3592" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3592" uniqueCount="533">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-15T14:56:56+00:00</t>
+    <t>2023-06-15T15:17:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1448,10 +1448,7 @@
 </t>
   </si>
   <si>
-    <t>[DR] : Coordonnées téléphoniques spécifiques à l’usage de la BAL MSS.</t>
-  </si>
-  <si>
-    <t>mailBoxMSS.phone</t>
+    <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
   </si>
   <si>
     <t>Organization.address</t>
@@ -1656,9 +1653,6 @@
   </si>
   <si>
     <t>Organization.contact.telecom</t>
-  </si>
-  <si>
-    <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
   </si>
   <si>
     <t>People have (primary) ways to contact them in some way such as phone, email.</t>
@@ -11529,7 +11523,7 @@
         <v>407</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>456</v>
+        <v>408</v>
       </c>
       <c r="O93" t="s" s="2">
         <v>409</v>
@@ -11598,10 +11592,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11624,19 +11618,19 @@
         <v>35</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>35</v>
@@ -11685,7 +11679,7 @@
         <v>35</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>36</v>
@@ -11697,15 +11691,15 @@
         <v>54</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11728,19 +11722,19 @@
         <v>43</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="N95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>35</v>
@@ -11789,7 +11783,7 @@
         <v>35</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>36</v>
@@ -11806,10 +11800,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11906,10 +11900,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12008,10 +12002,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12037,13 +12031,13 @@
         <v>56</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -12093,16 +12087,16 @@
         <v>35</v>
       </c>
       <c r="AF98" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI98" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>81</v>
@@ -12110,10 +12104,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12139,13 +12133,13 @@
         <v>89</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12174,7 +12168,7 @@
         <v>105</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Z99" t="s" s="2">
         <v>288</v>
@@ -12195,7 +12189,7 @@
         <v>35</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>36</v>
@@ -12212,10 +12206,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12241,13 +12235,13 @@
         <v>216</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -12297,7 +12291,7 @@
         <v>35</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>36</v>
@@ -12314,10 +12308,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12343,13 +12337,13 @@
         <v>56</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -12399,7 +12393,7 @@
         <v>35</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>36</v>
@@ -12416,10 +12410,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12442,19 +12436,19 @@
         <v>35</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="N102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>35</v>
@@ -12503,7 +12497,7 @@
         <v>35</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>36</v>
@@ -12520,10 +12514,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12620,10 +12614,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12722,14 +12716,14 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -12751,10 +12745,10 @@
         <v>62</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>65</v>
@@ -12809,7 +12803,7 @@
         <v>35</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>36</v>
@@ -12826,10 +12820,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12855,16 +12849,16 @@
         <v>234</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="N106" t="s" s="2">
+      <c r="O106" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>35</v>
@@ -12892,11 +12886,11 @@
         <v>105</v>
       </c>
       <c r="Y106" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="Z106" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="Z106" t="s" s="2">
-        <v>513</v>
-      </c>
       <c r="AA106" t="s" s="2">
         <v>35</v>
       </c>
@@ -12913,7 +12907,7 @@
         <v>35</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>36</v>
@@ -12930,10 +12924,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12956,19 +12950,19 @@
         <v>35</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>35</v>
@@ -13017,7 +13011,7 @@
         <v>35</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>36</v>
@@ -13034,10 +13028,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13063,14 +13057,14 @@
         <v>405</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>521</v>
+        <v>455</v>
       </c>
       <c r="M108" t="s" s="2">
         <v>407</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>35</v>
@@ -13119,7 +13113,7 @@
         <v>35</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>36</v>
@@ -13131,15 +13125,15 @@
         <v>54</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13162,19 +13156,19 @@
         <v>35</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N109" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="O109" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>35</v>
@@ -13223,7 +13217,7 @@
         <v>35</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>36</v>
@@ -13240,10 +13234,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13266,19 +13260,19 @@
         <v>35</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>35</v>
@@ -13327,7 +13321,7 @@
         <v>35</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>36</v>

--- a/ig/nr-change-mss-Org/StructureDefinition-as-organization.xlsx
+++ b/ig/nr-change-mss-Org/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-15T15:17:55+00:00</t>
+    <t>2023-06-15T15:23:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
